--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0227.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0227.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Số lượng Droid Hỗ Trợ của &lt;color=Highlight&gt;Guided Missile Protocol&lt;/color&gt; tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>Số lượng Droid Hỗ Trợ của &lt;color=Highlight&gt;Giao Thức Tên Lửa Điều Khiển&lt;/color&gt; tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Năng lượng cần để kích hoạt &lt;color=Highlight&gt;Boost&lt;/color&gt; giảm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>Năng lượng cần để kích hoạt &lt;color=Highlight&gt;Tăng Cường&lt;/color&gt; giảm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Số Lượng Rover Hỗ Trợ +{0}</t>
+          <t>Số Lượng Vận Mệnh Giả Hỗ Trợ +{0}</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Số Lượng Rover Hỗ Trợ tăng trong {0} giây</t>
+          <t>Số Lượng Vận Mệnh Giả Hỗ Trợ tăng trong {0} giây</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Tổng năng lượng dự trữ của xe máy. Bạn có thể sử dụng Boost để tăng tốc xe, nhưng sẽ tiêu hao Năng Lượng.</t>
+          <t>Tổng năng lượng dự trữ của xe máy. Bạn có thể dùng Boost để tăng tốc xe, nhưng sẽ tiêu hao Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3503,7 @@
       <c r="M47" t="inlineStr">
         <is>
           <t>Hiệu ứng nâng cấp:
-Sau khi kích hoạt Ram Dynamics, Cộng Hưởng Giả trong đội tăng 5% Tốc Độ Tích Lũy Tần Số Lệch trong 30 giây.</t>
+Sau khi kích hoạt Ram Dynamics, Resonator trong đội tăng 5% Tốc Độ Tích Lũy Tần Số Lệch trong 30 giây.</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3570,7 @@
       <c r="M48" t="inlineStr">
         <is>
           <t>Hiệu ứng nâng cấp:
-Sau khi kích hoạt Ram Dynamics, Cộng Hưởng Giả trong đội nhận Khiên tương đương 100% Lực Trường của xe máy.</t>
+Sau khi kích hoạt Ram Dynamics, Resonator trong đội nhận Khiên tương đương 100% Lực Trường của xe máy.</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3637,7 @@
       <c r="M49" t="inlineStr">
         <is>
           <t>Hiệu ứng nâng cấp:
-Khi chịu ảnh hưởng của Bão Hư Không, Cộng Hưởng Giả trong đội tăng 10% Tốc Độ Tích Lũy Lệch Pha.</t>
+Khi chịu ảnh hưởng của Bão Hư Không, Resonator trong đội tăng 10% Tốc Độ Tích Lũy Lệch Pha.</t>
         </is>
       </c>
     </row>
@@ -3837,8 +3837,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Hiệu ứng Nâng cấp:
-Tăng tỷ lệ rơi Echo ở Lahai-Roi.</t>
+          <t>Hiệu ứng Nâng cấp: Increases the Echo drop rate in Lahai-Roi.</t>
         </is>
       </c>
     </row>
@@ -3968,7 +3967,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Mỗi Cộng Hưởng Giả hoặc Vũ Khí 5 sao nhận được sẽ cấp 100 Điểm Hành Trình.</t>
+          <t>Mỗi Resonator hoặc Vũ Khí 5 sao nhận được sẽ cấp 100 Điểm Hành Trình.</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4812,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Khi chịu ảnh hưởng của Bão Hư Không, Tăng Cường Vỡ Tần Số của Cộng Hưởng Giả trong đội tăng thêm 20.</t>
+          <t>Khi chịu ảnh hưởng của Bão Hư Không, Tăng Cường Vỡ Tần Số của Resonator trong đội tăng thêm 20.</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4877,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Khi chịu ảnh hưởng của Bão Hư Không, Tăng Cường Vỡ Tần Số của Cộng Hưởng Giả trong đội tăng thêm 40.</t>
+          <t>Khi chịu ảnh hưởng của Bão Hư Không, Tăng Cường Vỡ Tần Số của Resonator trong đội tăng thêm 40.</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4942,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Tăng Tăng Tốc Đột Phá của các Cộng Hưởng Giả trong đội lên 15.</t>
+          <t>Tăng Tăng Tốc Đột Phá của các Resonator trong đội lên 15.</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5007,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Tăng Tăng Tốc Đột Phá của các Cộng Hưởng Giả trong đội lên 30.</t>
+          <t>Tăng Tăng Tốc Đột Phá của các Resonator trong đội lên 30.</t>
         </is>
       </c>
     </row>
@@ -5073,7 +5072,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Khi chịu ảnh hưởng của Bão Hư Không, Cộng Hưởng Giả trong đội nhận được Tăng Cường Phá Vỡ Tần Số.</t>
+          <t>Khi chịu ảnh hưởng của Bão Hư Không, Resonator trong đội nhận được Tăng Cường Phá Vỡ Tần Số.</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5137,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả trong đội nhận Tăng Cường Hiệu Ứng Phá Nhịp.</t>
+          <t>Resonator trong đội nhận Tăng Cường Hiệu Ứng Phá Nhịp.</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5529,7 @@
       <c r="M78" t="inlineStr">
         <is>
           <t>Hiệu ứng nâng cấp:
-Khi chịu ảnh hưởng của Bão Hư Không, Cộng Hưởng Giả trong đội tăng 20 điểm Tăng Cường Vỡ Pha.</t>
+Khi chịu ảnh hưởng của Bão Hư Không, Resonator trong đội tăng 20 điểm Tăng Cường Vỡ Pha.</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5596,7 @@
       <c r="M79" t="inlineStr">
         <is>
           <t>Hiệu ứng Nâng cấp:
-Tăng 15 điểm Tăng Cường Phá Tần cho Cộng Hưởng Giả trong đội.</t>
+Tăng 15 điểm Tăng Cường Phá Tần cho Resonator trong đội.</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7095,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>"Muốn ngồi lên ngai vàng, phải chịu được cái lạnh của nó— ối, kéo ta một cái! Ta dính chặt vào ghế rồi!"</t>
+          <t>"Muốn ngồi lên ngai vàng, phải chịu được cái lạnh của nó— ối, kéo tao một cái! Tao dính chặt vào ghế rồi!"</t>
         </is>
       </c>
     </row>
@@ -18298,7 +18297,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Remaining: {0}</t>
+          <t>Còn lại: {0}</t>
         </is>
       </c>
     </row>
@@ -23372,7 +23371,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Bộ Lọc Hiệu Ứng Sonata: &lt;color=HighlightB&gt;Tất cả&lt;/color&gt;</t>
+          <t>Bộ Lọc Hiệu Ứng Sonata: &lt;color=HighlightB&gt;Tất Cả&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -23697,7 +23696,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Completed: {0}/{1}</t>
+          <t>Hoàn thành: {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -23957,7 +23956,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả trong đội miễn nhiễm với đòn chí mạng một lần.</t>
+          <t>Resonator trong đội miễn nhiễm với đòn chí mạng một lần.</t>
         </is>
       </c>
     </row>
@@ -24615,7 +24614,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Total Points: {0}</t>
+          <t>Tổng Điểm: {0}</t>
         </is>
       </c>
     </row>
@@ -24875,7 +24874,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Round {0}</t>
+          <t>Vòng {0}</t>
         </is>
       </c>
     </row>
@@ -25005,7 +25004,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Round {0}</t>
+          <t>Vòng {0}</t>
         </is>
       </c>
     </row>
@@ -25590,7 +25589,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>&lt;color=#6c818a&gt;{0}&lt;/color&gt;&lt;color=#ffffff&gt;{1}&lt;/color&gt;</t>
+          <t>{0}{1}</t>
         </is>
       </c>
     </row>
@@ -29425,7 +29424,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>R?i ?i.</t>
+          <t>Rời đi.</t>
         </is>
       </c>
     </row>
